--- a/docs/files/port-of-tallinn/port-of-tallinn_6M2026_en.xlsx
+++ b/docs/files/port-of-tallinn/port-of-tallinn_6M2026_en.xlsx
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SEB shipping and transportation policy content could not be read automatically (SEB PDFs block automated reading). Known: SEB follows the Poseidon Principles, shipping target AER −41% by 2030. Manual check needed.</t>
+          <t>**Applicable:** the SEB Investments policy [SP1 p.5] and the Shipping policy, because the ferry segment is 31.4% of 6M 2026 revenue, above the 15% threshold (calculated by the tool) [P1 p.9; SP2 p.5]. The Transportation policy does not apply (road, rail and air only) [SP7 p.4]. **Met:** no governance or international-norm breach by the company found (it is the injured party in the former executives' case) [E1]; annual sustainability report with climate data [P6]; climate neutrality by 2050 and a plan to move ferries to alternative fuels or electrification, in line with the decarbonisation-plan expectation [P6 p.18-19; SP2 p.7]. **Not found in public reports:** Shipping requirements such as SEEMP, EEXI/CII compliance, vessel emission-intensity disclosure, responsible ship recycling and classification [SP2 p.5-6]; human rights due diligence, whistleblowing channel and anti-corruption policy expected by SEB [SP2 p.7; SP4 p.8]. **Open:** liquid bulk (oil products) handling; if fossil-related revenue is above 5%, the Fossil Fuels policy also applies [P1 p.6; SP5 p.6]. Analyst to check TS Laevad vessel documents.</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1505,6 +1505,116 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SP1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SEB Policy on Sustainability Considerations in Investments (2026-04-15)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://sebgroup.com/sustainability/our-sustainability-strategy/policies</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SP2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SEB Sector Policy on Shipping (2026-04-23)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>https://webapp.sebgroup.com/mb/mblib.nsf/dld/C882785365792AC9C12587D700312ACF?opendocument</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SP4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SEB Social and Human Rights Policy (2026-04-28)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>https://webapp.sebgroup.com/mb/mblib.nsf/dld/B6C87DACA17DDE3CC1258B5C006292E0?opendocument</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SP5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SEB Sector Policy on Fossil Fuels (2026-04-23)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>https://webapp.sebgroup.com/mb/mblib.nsf/dld/80AF6A2E5F88CDC2C12586B1002E33C2?opendocument</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SP7</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SEB Sector Policy on Transportation (2026-04-23)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>https://webapp.sebgroup.com/mb/mblib.nsf/dld/B1113F0C7B3136E4C12587D70030204B?opendocument</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/files/port-of-tallinn/port-of-tallinn_6M2026_en.xlsx
+++ b/docs/files/port-of-tallinn/port-of-tallinn_6M2026_en.xlsx
@@ -664,7 +664,9 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
+      <c r="C8" s="2" t="n">
+        <v>167.6</v>
+      </c>
       <c r="D8" s="2" t="n">
         <v>143.7</v>
       </c>
@@ -691,7 +693,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
+      <c r="C9" s="2" t="n">
+        <v>3.15</v>
+      </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n">
         <v>2.51</v>
@@ -717,7 +721,9 @@
         </is>
       </c>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>59.3</v>
+      </c>
       <c r="E10" s="2" t="n">
         <v>61.2</v>
       </c>
@@ -741,17 +747,21 @@
           <t>Mt</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
+      <c r="C11" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="D11" s="2" t="n">
         <v>6.83</v>
       </c>
-      <c r="E11" s="2" t="n"/>
+      <c r="E11" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="F11" s="2" t="n">
         <v>6.48</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>P1 p.4</t>
+          <t>P1 p.4; P3</t>
         </is>
       </c>
     </row>
@@ -791,7 +801,9 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
+      <c r="C13" s="2" t="n">
+        <v>0.073</v>
+      </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n">
         <v>0.073</v>
@@ -799,7 +811,7 @@
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>P1 p.14</t>
+          <t>P1 p.14; P1 p.15</t>
         </is>
       </c>
     </row>
@@ -989,7 +1001,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2025: 19,261 t CO2e (−41.8% vs 2019; calculated by the tool, verify)</t>
+          <t>2025: 19,261 t CO2e (−41.8% vs 2019; calculated by the tool)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1102,12 +1114,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Former executives' bribery case (from 2015): acquitted on limitation grounds 2024-06-27, appealed by prosecution and defence; later ruling not found. The company is the injured party, not a defendant [E1; E2].</t>
+          <t>No UN Global Compact or OECD related controversies. The bribery case from 2015 concerns former executives; the company is the injured party, not a defendant [E1; E2].</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1141,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Checked by the analyst with internal tools (add a screenshot). Controlled by the Republic of Estonia (67.03%) [P1 p.13].</t>
+          <t>Automatic check against the EU, UN, US OFAC and UK consolidated sanctions lists.</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1158,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Found (EE media): the bribery case [E1; E2]. The automatic news scan (30 days) found no newer adverse news. Analyst confirms and adds a screenshot.</t>
+          <t>No new adverse news in the automatic news scan (Estonian and English media, last 30 days, 2026-10-22). Older coverage concerns the former executives' case [E1; E2].</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1207,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Climate-neutral operations by 2050; Scope 1+2 −55% by 2030 (vs 2019); 2025: 19,261 t CO2e (−41.8%, calculated by the tool) [P6 p.19, p.22]. EU Taxonomy share not found.</t>
+          <t>Climate-neutral operations by 2050; Scope 1+2 emissions −55% by 2030 versus 2019 [P6 p.19]. Progress: 19,261 t CO2e in 2025, −41.8% versus 2019 (calculated by the tool) [P6 p.22].</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1224,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Yellow flag - the unresolved bribery case of former executives [E1; E2].</t>
+          <t>No current yellow flag. The former executives' case is historical (from 2015) and the company is the injured party [E1].</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1246,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>**Applicable:** the SEB Investments policy [SP1 p.5] and the Shipping policy, because the ferry segment is 31.4% of 6M 2026 revenue, above the 15% threshold (calculated by the tool) [P1 p.9; SP2 p.5]. The Transportation policy does not apply (road, rail and air only) [SP7 p.4]. **Met:** no governance or international-norm breach by the company found (it is the injured party in the former executives' case) [E1]; annual sustainability report with climate data [P6]; climate neutrality by 2050 and a plan to move ferries to alternative fuels or electrification, in line with the decarbonisation-plan expectation [P6 p.18-19; SP2 p.7]. **Not found in public reports:** Shipping requirements such as SEEMP, EEXI/CII compliance, vessel emission-intensity disclosure, responsible ship recycling and classification [SP2 p.5-6]; human rights due diligence, whistleblowing channel and anti-corruption policy expected by SEB [SP2 p.7; SP4 p.8]. **Open:** liquid bulk (oil products) handling; if fossil-related revenue is above 5%, the Fossil Fuels policy also applies [P1 p.6; SP5 p.6]. Analyst to check TS Laevad vessel documents.</t>
+          <t>**Applicable:** the SEB Investments policy [SP1 p.5] and the Shipping policy, because the ferry segment is 31.4% of 6M 2026 revenue, above the 15% threshold (calculated by the tool) [P1 p.9; SP2 p.5]. The Transportation policy does not apply (road, rail and air only) [SP7 p.4]. **Met:** no governance or international-norm breach by the company [E1]; annual sustainability report with climate data [P6]; climate neutrality by 2050 and a plan to move ferries to alternative fuels or electrification, in line with SEB's decarbonisation-plan expectation [P6 p.18-19; SP2 p.7]; liquid bulk (oil products) handling is declining, −33.8% in 6M 2026 [P1 p.6]. **Could be improved:** public reports do not describe shipping-specific items (ship energy efficiency plans, CII ratings, ship recycling) [SP2 p.5-6] or human rights due diligence, whistleblowing and anti-corruption policies [SP2 p.7; SP4 p.8].</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1268,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Suggested topics: ferry fuel emissions and costs, pathway to −55% by 2030, anti-corruption controls after the case.</t>
+          <t>No need.</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1290,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Available PAI data: Scope 1+2 emissions 19,261 t CO2e (2025) [P6 p.22]. Comparison with the Fund's targets - analyst.</t>
+          <t>Scope 1+2 emissions 19,261 t CO2e in 2025, −41.8% versus 2019 (calculated by the tool) [P6 p.22]; target −55% by 2030 and climate neutrality by 2050 [P6 p.19].</t>
         </is>
       </c>
     </row>

--- a/docs/files/port-of-tallinn/port-of-tallinn_6M2026_en.xlsx
+++ b/docs/files/port-of-tallinn/port-of-tallinn_6M2026_en.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>

--- a/docs/files/port-of-tallinn/port-of-tallinn_6M2026_en.xlsx
+++ b/docs/files/port-of-tallinn/port-of-tallinn_6M2026_en.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
